--- a/Result/profitability/1227.xlsx
+++ b/Result/profitability/1227.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0.48875</v>
+        <v>0.45625</v>
       </c>
       <c r="N2" t="n">
-        <v>26.19875</v>
+        <v>25.88625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.75</v>
       </c>
       <c r="M3" t="n">
-        <v>0.515</v>
+        <v>0.485</v>
       </c>
       <c r="N3" t="n">
-        <v>27.65</v>
+        <v>27.49375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,13 +899,13 @@
         <v>0.45</v>
       </c>
       <c r="M4" t="n">
-        <v>0.50625</v>
+        <v>0.4925</v>
       </c>
       <c r="N4" t="n">
-        <v>29.1175</v>
+        <v>28.84875</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0.45875</v>
+        <v>0.4775</v>
       </c>
       <c r="N5" t="n">
-        <v>29.53375</v>
+        <v>29.02125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.08</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5775</v>
+        <v>0.56125</v>
       </c>
       <c r="N6" t="n">
-        <v>30.91625</v>
+        <v>30.93625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.79</v>
       </c>
       <c r="M7" t="n">
-        <v>0.625</v>
+        <v>0.6112500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>32.98125</v>
+        <v>32.985</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.05</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7075</v>
+        <v>0.6775</v>
       </c>
       <c r="N8" t="n">
-        <v>35.23375</v>
+        <v>35.20625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>1.12</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7825000000000001</v>
+        <v>0.7825</v>
       </c>
       <c r="N9" t="n">
         <v>37.40625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1227</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>6163</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4732</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1431</v>
+      </c>
+      <c r="F75" t="n">
+        <v>23.22</v>
+      </c>
+      <c r="G75" t="n">
+        <v>43</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.70%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>217</v>
+      </c>
+      <c r="J75" t="n">
+        <v>260</v>
+      </c>
+      <c r="K75" t="n">
+        <v>254</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.3975000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>24.47375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.4615384615384615</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.2200000000000024</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.009385665529010323</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.153846153846154</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.100000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1500732064421669</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
